--- a/docs/test-plans/qapulse-functional-tests.xlsx
+++ b/docs/test-plans/qapulse-functional-tests.xlsx
@@ -1844,7 +1844,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="en-US"/>
               </a:p>
@@ -2190,7 +2190,7 @@
                 </a:defRPr>
               </a:pPr>
               <a:r>
-                <a:t/>
+                <a:t>None</a:t>
               </a:r>
               <a:endParaRPr lang="en-US"/>
             </a:p>
@@ -2267,7 +2267,7 @@
                 </a:defRPr>
               </a:pPr>
               <a:r>
-                <a:t/>
+                <a:t>None</a:t>
               </a:r>
               <a:endParaRPr lang="en-US"/>
             </a:p>
@@ -2300,7 +2300,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -2404,7 +2404,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -2458,7 +2458,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="en-US"/>
         </a:p>
@@ -4074,7 +4074,11 @@
       </c>
       <c r="J2" s="177" t="inlineStr"/>
       <c r="K2" s="177" t="inlineStr"/>
-      <c r="L2" s="177" t="inlineStr"/>
+      <c r="L2" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:18</t>
+        </is>
+      </c>
       <c r="M2" s="177" t="inlineStr"/>
     </row>
     <row r="3">
@@ -4123,7 +4127,11 @@
       </c>
       <c r="J3" s="177" t="inlineStr"/>
       <c r="K3" s="177" t="inlineStr"/>
-      <c r="L3" s="177" t="inlineStr"/>
+      <c r="L3" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:33</t>
+        </is>
+      </c>
       <c r="M3" s="177" t="inlineStr"/>
     </row>
     <row r="4">
@@ -4170,7 +4178,11 @@
       </c>
       <c r="J4" s="177" t="inlineStr"/>
       <c r="K4" s="177" t="inlineStr"/>
-      <c r="L4" s="177" t="inlineStr"/>
+      <c r="L4" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:53</t>
+        </is>
+      </c>
       <c r="M4" s="177" t="inlineStr"/>
     </row>
     <row r="5">
@@ -4219,7 +4231,11 @@
       </c>
       <c r="J5" s="177" t="inlineStr"/>
       <c r="K5" s="177" t="inlineStr"/>
-      <c r="L5" s="177" t="inlineStr"/>
+      <c r="L5" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:65</t>
+        </is>
+      </c>
       <c r="M5" s="177" t="inlineStr"/>
     </row>
     <row r="6">
@@ -4266,7 +4282,11 @@
       </c>
       <c r="J6" s="177" t="inlineStr"/>
       <c r="K6" s="177" t="inlineStr"/>
-      <c r="L6" s="177" t="inlineStr"/>
+      <c r="L6" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:91</t>
+        </is>
+      </c>
       <c r="M6" s="177" t="inlineStr"/>
     </row>
     <row r="7">
@@ -4315,7 +4335,11 @@
       </c>
       <c r="J7" s="177" t="inlineStr"/>
       <c r="K7" s="177" t="inlineStr"/>
-      <c r="L7" s="177" t="inlineStr"/>
+      <c r="L7" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:112</t>
+        </is>
+      </c>
       <c r="M7" s="177" t="inlineStr"/>
     </row>
     <row r="8">
@@ -4363,7 +4387,11 @@
       </c>
       <c r="J8" s="177" t="inlineStr"/>
       <c r="K8" s="177" t="inlineStr"/>
-      <c r="L8" s="177" t="inlineStr"/>
+      <c r="L8" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:124</t>
+        </is>
+      </c>
       <c r="M8" s="177" t="inlineStr"/>
     </row>
     <row r="9">
@@ -4411,7 +4439,11 @@
       </c>
       <c r="J9" s="177" t="inlineStr"/>
       <c r="K9" s="177" t="inlineStr"/>
-      <c r="L9" s="177" t="inlineStr"/>
+      <c r="L9" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:137</t>
+        </is>
+      </c>
       <c r="M9" s="177" t="inlineStr"/>
     </row>
     <row r="10">
@@ -4460,7 +4492,11 @@
       </c>
       <c r="J10" s="177" t="inlineStr"/>
       <c r="K10" s="177" t="inlineStr"/>
-      <c r="L10" s="177" t="inlineStr"/>
+      <c r="L10" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:157</t>
+        </is>
+      </c>
       <c r="M10" s="177" t="inlineStr"/>
     </row>
     <row r="11">
@@ -4507,7 +4543,11 @@
       </c>
       <c r="J11" s="177" t="inlineStr"/>
       <c r="K11" s="177" t="inlineStr"/>
-      <c r="L11" s="177" t="inlineStr"/>
+      <c r="L11" s="177" t="inlineStr">
+        <is>
+          <t>Manual (declared in spec as skip) — artifacts/qa-automation/tests/functional.spec.ts:180</t>
+        </is>
+      </c>
       <c r="M11" s="177" t="inlineStr"/>
     </row>
     <row r="12">
@@ -4556,7 +4596,11 @@
       </c>
       <c r="J12" s="177" t="inlineStr"/>
       <c r="K12" s="177" t="inlineStr"/>
-      <c r="L12" s="177" t="inlineStr"/>
+      <c r="L12" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:186</t>
+        </is>
+      </c>
       <c r="M12" s="177" t="inlineStr"/>
     </row>
     <row r="13">
@@ -4605,7 +4649,11 @@
       </c>
       <c r="J13" s="177" t="inlineStr"/>
       <c r="K13" s="177" t="inlineStr"/>
-      <c r="L13" s="177" t="inlineStr"/>
+      <c r="L13" s="177" t="inlineStr">
+        <is>
+          <t>Manual (declared in spec as skip) — artifacts/qa-automation/tests/functional.spec.ts:218</t>
+        </is>
+      </c>
       <c r="M13" s="177" t="inlineStr"/>
     </row>
     <row r="14">
@@ -4652,7 +4700,11 @@
       </c>
       <c r="J14" s="177" t="inlineStr"/>
       <c r="K14" s="177" t="inlineStr"/>
-      <c r="L14" s="177" t="inlineStr"/>
+      <c r="L14" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:226</t>
+        </is>
+      </c>
       <c r="M14" s="177" t="inlineStr"/>
     </row>
     <row r="15">
@@ -4701,7 +4753,11 @@
       </c>
       <c r="J15" s="177" t="inlineStr"/>
       <c r="K15" s="177" t="inlineStr"/>
-      <c r="L15" s="177" t="inlineStr"/>
+      <c r="L15" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:249</t>
+        </is>
+      </c>
       <c r="M15" s="177" t="inlineStr"/>
     </row>
     <row r="16">
@@ -4749,7 +4805,11 @@
       </c>
       <c r="J16" s="177" t="inlineStr"/>
       <c r="K16" s="177" t="inlineStr"/>
-      <c r="L16" s="177" t="inlineStr"/>
+      <c r="L16" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:279</t>
+        </is>
+      </c>
       <c r="M16" s="177" t="inlineStr"/>
     </row>
     <row r="17">
@@ -4797,7 +4857,11 @@
       </c>
       <c r="J17" s="177" t="inlineStr"/>
       <c r="K17" s="177" t="inlineStr"/>
-      <c r="L17" s="177" t="inlineStr"/>
+      <c r="L17" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:299</t>
+        </is>
+      </c>
       <c r="M17" s="177" t="inlineStr"/>
     </row>
     <row r="18">
@@ -4845,7 +4909,11 @@
       </c>
       <c r="J18" s="177" t="inlineStr"/>
       <c r="K18" s="177" t="inlineStr"/>
-      <c r="L18" s="177" t="inlineStr"/>
+      <c r="L18" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:322</t>
+        </is>
+      </c>
       <c r="M18" s="177" t="inlineStr"/>
     </row>
     <row r="19">
@@ -4892,7 +4960,11 @@
       </c>
       <c r="J19" s="177" t="inlineStr"/>
       <c r="K19" s="177" t="inlineStr"/>
-      <c r="L19" s="177" t="inlineStr"/>
+      <c r="L19" s="177" t="inlineStr">
+        <is>
+          <t>Manual (declared in spec as skip) — artifacts/qa-automation/tests/functional.spec.ts:344</t>
+        </is>
+      </c>
       <c r="M19" s="177" t="inlineStr"/>
     </row>
     <row r="20">
@@ -4939,7 +5011,11 @@
       </c>
       <c r="J20" s="177" t="inlineStr"/>
       <c r="K20" s="177" t="inlineStr"/>
-      <c r="L20" s="177" t="inlineStr"/>
+      <c r="L20" s="177" t="inlineStr">
+        <is>
+          <t>Manual (declared in spec as skip) — artifacts/qa-automation/tests/functional.spec.ts:350</t>
+        </is>
+      </c>
       <c r="M20" s="177" t="inlineStr"/>
     </row>
     <row r="21">
@@ -4987,7 +5063,11 @@
       </c>
       <c r="J21" s="177" t="inlineStr"/>
       <c r="K21" s="177" t="inlineStr"/>
-      <c r="L21" s="177" t="inlineStr"/>
+      <c r="L21" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:356</t>
+        </is>
+      </c>
       <c r="M21" s="177" t="inlineStr"/>
     </row>
     <row r="22">
@@ -5035,7 +5115,11 @@
       </c>
       <c r="J22" s="177" t="inlineStr"/>
       <c r="K22" s="177" t="inlineStr"/>
-      <c r="L22" s="177" t="inlineStr"/>
+      <c r="L22" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:407</t>
+        </is>
+      </c>
       <c r="M22" s="177" t="inlineStr"/>
     </row>
     <row r="23">
@@ -5083,7 +5167,11 @@
       </c>
       <c r="J23" s="177" t="inlineStr"/>
       <c r="K23" s="177" t="inlineStr"/>
-      <c r="L23" s="177" t="inlineStr"/>
+      <c r="L23" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:427</t>
+        </is>
+      </c>
       <c r="M23" s="177" t="inlineStr"/>
     </row>
     <row r="24">
@@ -5131,7 +5219,11 @@
       </c>
       <c r="J24" s="177" t="inlineStr"/>
       <c r="K24" s="177" t="inlineStr"/>
-      <c r="L24" s="177" t="inlineStr"/>
+      <c r="L24" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:446</t>
+        </is>
+      </c>
       <c r="M24" s="177" t="inlineStr"/>
     </row>
     <row r="25">
@@ -5178,7 +5270,11 @@
       </c>
       <c r="J25" s="177" t="inlineStr"/>
       <c r="K25" s="177" t="inlineStr"/>
-      <c r="L25" s="177" t="inlineStr"/>
+      <c r="L25" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:465</t>
+        </is>
+      </c>
       <c r="M25" s="177" t="inlineStr"/>
     </row>
     <row r="26">
@@ -5225,7 +5321,11 @@
       </c>
       <c r="J26" s="177" t="inlineStr"/>
       <c r="K26" s="177" t="inlineStr"/>
-      <c r="L26" s="177" t="inlineStr"/>
+      <c r="L26" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:492</t>
+        </is>
+      </c>
       <c r="M26" s="177" t="inlineStr"/>
     </row>
     <row r="27">
@@ -5274,7 +5374,11 @@
       </c>
       <c r="J27" s="177" t="inlineStr"/>
       <c r="K27" s="177" t="inlineStr"/>
-      <c r="L27" s="177" t="inlineStr"/>
+      <c r="L27" s="177" t="inlineStr">
+        <is>
+          <t>Manual (declared in spec as skip) — artifacts/qa-automation/tests/functional.spec.ts:507</t>
+        </is>
+      </c>
       <c r="M27" s="177" t="inlineStr"/>
     </row>
     <row r="28">
@@ -5321,7 +5425,11 @@
       </c>
       <c r="J28" s="177" t="inlineStr"/>
       <c r="K28" s="177" t="inlineStr"/>
-      <c r="L28" s="177" t="inlineStr"/>
+      <c r="L28" s="177" t="inlineStr">
+        <is>
+          <t>Manual (declared in spec as skip) — artifacts/qa-automation/tests/functional.spec.ts:515</t>
+        </is>
+      </c>
       <c r="M28" s="177" t="inlineStr"/>
     </row>
     <row r="29">
@@ -5368,7 +5476,11 @@
       </c>
       <c r="J29" s="177" t="inlineStr"/>
       <c r="K29" s="177" t="inlineStr"/>
-      <c r="L29" s="177" t="inlineStr"/>
+      <c r="L29" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:521</t>
+        </is>
+      </c>
       <c r="M29" s="177" t="inlineStr"/>
     </row>
     <row r="30">
@@ -5416,7 +5528,11 @@
       </c>
       <c r="J30" s="177" t="inlineStr"/>
       <c r="K30" s="177" t="inlineStr"/>
-      <c r="L30" s="177" t="inlineStr"/>
+      <c r="L30" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:541</t>
+        </is>
+      </c>
       <c r="M30" s="177" t="inlineStr"/>
     </row>
     <row r="31">
@@ -5464,7 +5580,11 @@
       </c>
       <c r="J31" s="177" t="inlineStr"/>
       <c r="K31" s="177" t="inlineStr"/>
-      <c r="L31" s="177" t="inlineStr"/>
+      <c r="L31" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:585</t>
+        </is>
+      </c>
       <c r="M31" s="177" t="inlineStr"/>
     </row>
     <row r="32">
@@ -5511,7 +5631,11 @@
       </c>
       <c r="J32" s="177" t="inlineStr"/>
       <c r="K32" s="177" t="inlineStr"/>
-      <c r="L32" s="177" t="inlineStr"/>
+      <c r="L32" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:616</t>
+        </is>
+      </c>
       <c r="M32" s="177" t="inlineStr"/>
     </row>
     <row r="33">
@@ -5559,7 +5683,11 @@
       </c>
       <c r="J33" s="177" t="inlineStr"/>
       <c r="K33" s="177" t="inlineStr"/>
-      <c r="L33" s="177" t="inlineStr"/>
+      <c r="L33" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:642</t>
+        </is>
+      </c>
       <c r="M33" s="177" t="inlineStr"/>
     </row>
     <row r="34">
@@ -5607,7 +5735,11 @@
       </c>
       <c r="J34" s="177" t="inlineStr"/>
       <c r="K34" s="177" t="inlineStr"/>
-      <c r="L34" s="177" t="inlineStr"/>
+      <c r="L34" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:665</t>
+        </is>
+      </c>
       <c r="M34" s="177" t="inlineStr"/>
     </row>
     <row r="35">
@@ -5654,7 +5786,11 @@
       </c>
       <c r="J35" s="177" t="inlineStr"/>
       <c r="K35" s="177" t="inlineStr"/>
-      <c r="L35" s="177" t="inlineStr"/>
+      <c r="L35" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:692</t>
+        </is>
+      </c>
       <c r="M35" s="177" t="inlineStr"/>
     </row>
     <row r="36">
@@ -5701,7 +5837,11 @@
       </c>
       <c r="J36" s="177" t="inlineStr"/>
       <c r="K36" s="177" t="inlineStr"/>
-      <c r="L36" s="177" t="inlineStr"/>
+      <c r="L36" s="177" t="inlineStr">
+        <is>
+          <t>Manual (declared in spec as skip) — artifacts/qa-automation/tests/functional.spec.ts:711</t>
+        </is>
+      </c>
       <c r="M36" s="177" t="inlineStr"/>
     </row>
     <row r="37">
@@ -5748,7 +5888,11 @@
       </c>
       <c r="J37" s="177" t="inlineStr"/>
       <c r="K37" s="177" t="inlineStr"/>
-      <c r="L37" s="177" t="inlineStr"/>
+      <c r="L37" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:719</t>
+        </is>
+      </c>
       <c r="M37" s="177" t="inlineStr"/>
     </row>
     <row r="38">
@@ -5795,7 +5939,11 @@
       </c>
       <c r="J38" s="177" t="inlineStr"/>
       <c r="K38" s="177" t="inlineStr"/>
-      <c r="L38" s="177" t="inlineStr"/>
+      <c r="L38" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:740</t>
+        </is>
+      </c>
       <c r="M38" s="177" t="inlineStr"/>
     </row>
     <row r="39">
@@ -5842,7 +5990,11 @@
       </c>
       <c r="J39" s="177" t="inlineStr"/>
       <c r="K39" s="177" t="inlineStr"/>
-      <c r="L39" s="177" t="inlineStr"/>
+      <c r="L39" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:756</t>
+        </is>
+      </c>
       <c r="M39" s="177" t="inlineStr"/>
     </row>
     <row r="40">
@@ -5889,7 +6041,11 @@
       </c>
       <c r="J40" s="177" t="inlineStr"/>
       <c r="K40" s="177" t="inlineStr"/>
-      <c r="L40" s="177" t="inlineStr"/>
+      <c r="L40" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:777</t>
+        </is>
+      </c>
       <c r="M40" s="177" t="inlineStr"/>
     </row>
     <row r="41">
@@ -5937,7 +6093,11 @@
       </c>
       <c r="J41" s="177" t="inlineStr"/>
       <c r="K41" s="177" t="inlineStr"/>
-      <c r="L41" s="177" t="inlineStr"/>
+      <c r="L41" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:806</t>
+        </is>
+      </c>
       <c r="M41" s="177" t="inlineStr"/>
     </row>
     <row r="42">
@@ -5984,7 +6144,11 @@
       </c>
       <c r="J42" s="177" t="inlineStr"/>
       <c r="K42" s="177" t="inlineStr"/>
-      <c r="L42" s="177" t="inlineStr"/>
+      <c r="L42" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:827</t>
+        </is>
+      </c>
       <c r="M42" s="177" t="inlineStr"/>
     </row>
     <row r="43">
@@ -6032,7 +6196,11 @@
       </c>
       <c r="J43" s="177" t="inlineStr"/>
       <c r="K43" s="177" t="inlineStr"/>
-      <c r="L43" s="177" t="inlineStr"/>
+      <c r="L43" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:845</t>
+        </is>
+      </c>
       <c r="M43" s="177" t="inlineStr"/>
     </row>
     <row r="44">
@@ -6080,7 +6248,11 @@
       </c>
       <c r="J44" s="177" t="inlineStr"/>
       <c r="K44" s="177" t="inlineStr"/>
-      <c r="L44" s="177" t="inlineStr"/>
+      <c r="L44" s="177" t="inlineStr">
+        <is>
+          <t>Manual (declared in spec as skip) — artifacts/qa-automation/tests/functional.spec.ts:872</t>
+        </is>
+      </c>
       <c r="M44" s="177" t="inlineStr"/>
     </row>
     <row r="45">
@@ -6127,7 +6299,11 @@
       </c>
       <c r="J45" s="177" t="inlineStr"/>
       <c r="K45" s="177" t="inlineStr"/>
-      <c r="L45" s="177" t="inlineStr"/>
+      <c r="L45" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:878</t>
+        </is>
+      </c>
       <c r="M45" s="177" t="inlineStr"/>
     </row>
     <row r="46">
@@ -6175,7 +6351,11 @@
       </c>
       <c r="J46" s="177" t="inlineStr"/>
       <c r="K46" s="177" t="inlineStr"/>
-      <c r="L46" s="177" t="inlineStr"/>
+      <c r="L46" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:906</t>
+        </is>
+      </c>
       <c r="M46" s="177" t="inlineStr"/>
     </row>
     <row r="47">
@@ -6222,7 +6402,11 @@
       </c>
       <c r="J47" s="177" t="inlineStr"/>
       <c r="K47" s="177" t="inlineStr"/>
-      <c r="L47" s="177" t="inlineStr"/>
+      <c r="L47" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:932</t>
+        </is>
+      </c>
       <c r="M47" s="177" t="inlineStr"/>
     </row>
     <row r="48">
@@ -6269,7 +6453,11 @@
       </c>
       <c r="J48" s="177" t="inlineStr"/>
       <c r="K48" s="177" t="inlineStr"/>
-      <c r="L48" s="177" t="inlineStr"/>
+      <c r="L48" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:951</t>
+        </is>
+      </c>
       <c r="M48" s="177" t="inlineStr"/>
     </row>
     <row r="49">
@@ -6317,7 +6505,11 @@
       </c>
       <c r="J49" s="177" t="inlineStr"/>
       <c r="K49" s="177" t="inlineStr"/>
-      <c r="L49" s="177" t="inlineStr"/>
+      <c r="L49" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:963</t>
+        </is>
+      </c>
       <c r="M49" s="177" t="inlineStr"/>
     </row>
     <row r="50">
@@ -6365,7 +6557,11 @@
       </c>
       <c r="J50" s="177" t="inlineStr"/>
       <c r="K50" s="177" t="inlineStr"/>
-      <c r="L50" s="177" t="inlineStr"/>
+      <c r="L50" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:991</t>
+        </is>
+      </c>
       <c r="M50" s="177" t="inlineStr"/>
     </row>
   </sheetData>

--- a/docs/test-plans/qapulse-functional-tests.xlsx
+++ b/docs/test-plans/qapulse-functional-tests.xlsx
@@ -1844,7 +1844,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t>None</a:t>
+                  <a:t/>
                 </a:r>
                 <a:endParaRPr lang="en-US"/>
               </a:p>
@@ -2190,7 +2190,7 @@
                 </a:defRPr>
               </a:pPr>
               <a:r>
-                <a:t>None</a:t>
+                <a:t/>
               </a:r>
               <a:endParaRPr lang="en-US"/>
             </a:p>
@@ -2267,7 +2267,7 @@
                 </a:defRPr>
               </a:pPr>
               <a:r>
-                <a:t>None</a:t>
+                <a:t/>
               </a:r>
               <a:endParaRPr lang="en-US"/>
             </a:p>
@@ -2300,7 +2300,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t>None</a:t>
+              <a:t/>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -2404,7 +2404,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t>None</a:t>
+              <a:t/>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -2458,7 +2458,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t>None</a:t>
+            <a:t/>
           </a:r>
           <a:endParaRPr lang="en-US"/>
         </a:p>
@@ -4074,11 +4074,7 @@
       </c>
       <c r="J2" s="177" t="inlineStr"/>
       <c r="K2" s="177" t="inlineStr"/>
-      <c r="L2" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:18</t>
-        </is>
-      </c>
+      <c r="L2" s="177" t="inlineStr"/>
       <c r="M2" s="177" t="inlineStr"/>
     </row>
     <row r="3">
@@ -4127,11 +4123,7 @@
       </c>
       <c r="J3" s="177" t="inlineStr"/>
       <c r="K3" s="177" t="inlineStr"/>
-      <c r="L3" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:33</t>
-        </is>
-      </c>
+      <c r="L3" s="177" t="inlineStr"/>
       <c r="M3" s="177" t="inlineStr"/>
     </row>
     <row r="4">
@@ -4178,11 +4170,7 @@
       </c>
       <c r="J4" s="177" t="inlineStr"/>
       <c r="K4" s="177" t="inlineStr"/>
-      <c r="L4" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:53</t>
-        </is>
-      </c>
+      <c r="L4" s="177" t="inlineStr"/>
       <c r="M4" s="177" t="inlineStr"/>
     </row>
     <row r="5">
@@ -4231,11 +4219,7 @@
       </c>
       <c r="J5" s="177" t="inlineStr"/>
       <c r="K5" s="177" t="inlineStr"/>
-      <c r="L5" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:65</t>
-        </is>
-      </c>
+      <c r="L5" s="177" t="inlineStr"/>
       <c r="M5" s="177" t="inlineStr"/>
     </row>
     <row r="6">
@@ -4282,11 +4266,7 @@
       </c>
       <c r="J6" s="177" t="inlineStr"/>
       <c r="K6" s="177" t="inlineStr"/>
-      <c r="L6" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:91</t>
-        </is>
-      </c>
+      <c r="L6" s="177" t="inlineStr"/>
       <c r="M6" s="177" t="inlineStr"/>
     </row>
     <row r="7">
@@ -4335,11 +4315,7 @@
       </c>
       <c r="J7" s="177" t="inlineStr"/>
       <c r="K7" s="177" t="inlineStr"/>
-      <c r="L7" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:112</t>
-        </is>
-      </c>
+      <c r="L7" s="177" t="inlineStr"/>
       <c r="M7" s="177" t="inlineStr"/>
     </row>
     <row r="8">
@@ -4387,11 +4363,7 @@
       </c>
       <c r="J8" s="177" t="inlineStr"/>
       <c r="K8" s="177" t="inlineStr"/>
-      <c r="L8" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:124</t>
-        </is>
-      </c>
+      <c r="L8" s="177" t="inlineStr"/>
       <c r="M8" s="177" t="inlineStr"/>
     </row>
     <row r="9">
@@ -4439,11 +4411,7 @@
       </c>
       <c r="J9" s="177" t="inlineStr"/>
       <c r="K9" s="177" t="inlineStr"/>
-      <c r="L9" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:137</t>
-        </is>
-      </c>
+      <c r="L9" s="177" t="inlineStr"/>
       <c r="M9" s="177" t="inlineStr"/>
     </row>
     <row r="10">
@@ -4492,11 +4460,7 @@
       </c>
       <c r="J10" s="177" t="inlineStr"/>
       <c r="K10" s="177" t="inlineStr"/>
-      <c r="L10" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:157</t>
-        </is>
-      </c>
+      <c r="L10" s="177" t="inlineStr"/>
       <c r="M10" s="177" t="inlineStr"/>
     </row>
     <row r="11">
@@ -4543,11 +4507,7 @@
       </c>
       <c r="J11" s="177" t="inlineStr"/>
       <c r="K11" s="177" t="inlineStr"/>
-      <c r="L11" s="177" t="inlineStr">
-        <is>
-          <t>Manual (declared in spec as skip) — artifacts/qa-automation/tests/functional.spec.ts:180</t>
-        </is>
-      </c>
+      <c r="L11" s="177" t="inlineStr"/>
       <c r="M11" s="177" t="inlineStr"/>
     </row>
     <row r="12">
@@ -4596,11 +4556,7 @@
       </c>
       <c r="J12" s="177" t="inlineStr"/>
       <c r="K12" s="177" t="inlineStr"/>
-      <c r="L12" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:186</t>
-        </is>
-      </c>
+      <c r="L12" s="177" t="inlineStr"/>
       <c r="M12" s="177" t="inlineStr"/>
     </row>
     <row r="13">
@@ -4649,11 +4605,7 @@
       </c>
       <c r="J13" s="177" t="inlineStr"/>
       <c r="K13" s="177" t="inlineStr"/>
-      <c r="L13" s="177" t="inlineStr">
-        <is>
-          <t>Manual (declared in spec as skip) — artifacts/qa-automation/tests/functional.spec.ts:218</t>
-        </is>
-      </c>
+      <c r="L13" s="177" t="inlineStr"/>
       <c r="M13" s="177" t="inlineStr"/>
     </row>
     <row r="14">
@@ -4700,11 +4652,7 @@
       </c>
       <c r="J14" s="177" t="inlineStr"/>
       <c r="K14" s="177" t="inlineStr"/>
-      <c r="L14" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:226</t>
-        </is>
-      </c>
+      <c r="L14" s="177" t="inlineStr"/>
       <c r="M14" s="177" t="inlineStr"/>
     </row>
     <row r="15">
@@ -4753,11 +4701,7 @@
       </c>
       <c r="J15" s="177" t="inlineStr"/>
       <c r="K15" s="177" t="inlineStr"/>
-      <c r="L15" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:249</t>
-        </is>
-      </c>
+      <c r="L15" s="177" t="inlineStr"/>
       <c r="M15" s="177" t="inlineStr"/>
     </row>
     <row r="16">
@@ -4805,11 +4749,7 @@
       </c>
       <c r="J16" s="177" t="inlineStr"/>
       <c r="K16" s="177" t="inlineStr"/>
-      <c r="L16" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:279</t>
-        </is>
-      </c>
+      <c r="L16" s="177" t="inlineStr"/>
       <c r="M16" s="177" t="inlineStr"/>
     </row>
     <row r="17">
@@ -4857,11 +4797,7 @@
       </c>
       <c r="J17" s="177" t="inlineStr"/>
       <c r="K17" s="177" t="inlineStr"/>
-      <c r="L17" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:299</t>
-        </is>
-      </c>
+      <c r="L17" s="177" t="inlineStr"/>
       <c r="M17" s="177" t="inlineStr"/>
     </row>
     <row r="18">
@@ -4909,11 +4845,7 @@
       </c>
       <c r="J18" s="177" t="inlineStr"/>
       <c r="K18" s="177" t="inlineStr"/>
-      <c r="L18" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:322</t>
-        </is>
-      </c>
+      <c r="L18" s="177" t="inlineStr"/>
       <c r="M18" s="177" t="inlineStr"/>
     </row>
     <row r="19">
@@ -4960,11 +4892,7 @@
       </c>
       <c r="J19" s="177" t="inlineStr"/>
       <c r="K19" s="177" t="inlineStr"/>
-      <c r="L19" s="177" t="inlineStr">
-        <is>
-          <t>Manual (declared in spec as skip) — artifacts/qa-automation/tests/functional.spec.ts:344</t>
-        </is>
-      </c>
+      <c r="L19" s="177" t="inlineStr"/>
       <c r="M19" s="177" t="inlineStr"/>
     </row>
     <row r="20">
@@ -5011,11 +4939,7 @@
       </c>
       <c r="J20" s="177" t="inlineStr"/>
       <c r="K20" s="177" t="inlineStr"/>
-      <c r="L20" s="177" t="inlineStr">
-        <is>
-          <t>Manual (declared in spec as skip) — artifacts/qa-automation/tests/functional.spec.ts:350</t>
-        </is>
-      </c>
+      <c r="L20" s="177" t="inlineStr"/>
       <c r="M20" s="177" t="inlineStr"/>
     </row>
     <row r="21">
@@ -5063,11 +4987,7 @@
       </c>
       <c r="J21" s="177" t="inlineStr"/>
       <c r="K21" s="177" t="inlineStr"/>
-      <c r="L21" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:356</t>
-        </is>
-      </c>
+      <c r="L21" s="177" t="inlineStr"/>
       <c r="M21" s="177" t="inlineStr"/>
     </row>
     <row r="22">
@@ -5115,11 +5035,7 @@
       </c>
       <c r="J22" s="177" t="inlineStr"/>
       <c r="K22" s="177" t="inlineStr"/>
-      <c r="L22" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:407</t>
-        </is>
-      </c>
+      <c r="L22" s="177" t="inlineStr"/>
       <c r="M22" s="177" t="inlineStr"/>
     </row>
     <row r="23">
@@ -5167,11 +5083,7 @@
       </c>
       <c r="J23" s="177" t="inlineStr"/>
       <c r="K23" s="177" t="inlineStr"/>
-      <c r="L23" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:427</t>
-        </is>
-      </c>
+      <c r="L23" s="177" t="inlineStr"/>
       <c r="M23" s="177" t="inlineStr"/>
     </row>
     <row r="24">
@@ -5219,11 +5131,7 @@
       </c>
       <c r="J24" s="177" t="inlineStr"/>
       <c r="K24" s="177" t="inlineStr"/>
-      <c r="L24" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:446</t>
-        </is>
-      </c>
+      <c r="L24" s="177" t="inlineStr"/>
       <c r="M24" s="177" t="inlineStr"/>
     </row>
     <row r="25">
@@ -5270,11 +5178,7 @@
       </c>
       <c r="J25" s="177" t="inlineStr"/>
       <c r="K25" s="177" t="inlineStr"/>
-      <c r="L25" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:465</t>
-        </is>
-      </c>
+      <c r="L25" s="177" t="inlineStr"/>
       <c r="M25" s="177" t="inlineStr"/>
     </row>
     <row r="26">
@@ -5321,11 +5225,7 @@
       </c>
       <c r="J26" s="177" t="inlineStr"/>
       <c r="K26" s="177" t="inlineStr"/>
-      <c r="L26" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:492</t>
-        </is>
-      </c>
+      <c r="L26" s="177" t="inlineStr"/>
       <c r="M26" s="177" t="inlineStr"/>
     </row>
     <row r="27">
@@ -5374,11 +5274,7 @@
       </c>
       <c r="J27" s="177" t="inlineStr"/>
       <c r="K27" s="177" t="inlineStr"/>
-      <c r="L27" s="177" t="inlineStr">
-        <is>
-          <t>Manual (declared in spec as skip) — artifacts/qa-automation/tests/functional.spec.ts:507</t>
-        </is>
-      </c>
+      <c r="L27" s="177" t="inlineStr"/>
       <c r="M27" s="177" t="inlineStr"/>
     </row>
     <row r="28">
@@ -5425,11 +5321,7 @@
       </c>
       <c r="J28" s="177" t="inlineStr"/>
       <c r="K28" s="177" t="inlineStr"/>
-      <c r="L28" s="177" t="inlineStr">
-        <is>
-          <t>Manual (declared in spec as skip) — artifacts/qa-automation/tests/functional.spec.ts:515</t>
-        </is>
-      </c>
+      <c r="L28" s="177" t="inlineStr"/>
       <c r="M28" s="177" t="inlineStr"/>
     </row>
     <row r="29">
@@ -5476,11 +5368,7 @@
       </c>
       <c r="J29" s="177" t="inlineStr"/>
       <c r="K29" s="177" t="inlineStr"/>
-      <c r="L29" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:521</t>
-        </is>
-      </c>
+      <c r="L29" s="177" t="inlineStr"/>
       <c r="M29" s="177" t="inlineStr"/>
     </row>
     <row r="30">
@@ -5528,11 +5416,7 @@
       </c>
       <c r="J30" s="177" t="inlineStr"/>
       <c r="K30" s="177" t="inlineStr"/>
-      <c r="L30" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:541</t>
-        </is>
-      </c>
+      <c r="L30" s="177" t="inlineStr"/>
       <c r="M30" s="177" t="inlineStr"/>
     </row>
     <row r="31">
@@ -5580,11 +5464,7 @@
       </c>
       <c r="J31" s="177" t="inlineStr"/>
       <c r="K31" s="177" t="inlineStr"/>
-      <c r="L31" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:585</t>
-        </is>
-      </c>
+      <c r="L31" s="177" t="inlineStr"/>
       <c r="M31" s="177" t="inlineStr"/>
     </row>
     <row r="32">
@@ -5631,11 +5511,7 @@
       </c>
       <c r="J32" s="177" t="inlineStr"/>
       <c r="K32" s="177" t="inlineStr"/>
-      <c r="L32" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:616</t>
-        </is>
-      </c>
+      <c r="L32" s="177" t="inlineStr"/>
       <c r="M32" s="177" t="inlineStr"/>
     </row>
     <row r="33">
@@ -5683,11 +5559,7 @@
       </c>
       <c r="J33" s="177" t="inlineStr"/>
       <c r="K33" s="177" t="inlineStr"/>
-      <c r="L33" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:642</t>
-        </is>
-      </c>
+      <c r="L33" s="177" t="inlineStr"/>
       <c r="M33" s="177" t="inlineStr"/>
     </row>
     <row r="34">
@@ -5735,11 +5607,7 @@
       </c>
       <c r="J34" s="177" t="inlineStr"/>
       <c r="K34" s="177" t="inlineStr"/>
-      <c r="L34" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:665</t>
-        </is>
-      </c>
+      <c r="L34" s="177" t="inlineStr"/>
       <c r="M34" s="177" t="inlineStr"/>
     </row>
     <row r="35">
@@ -5786,11 +5654,7 @@
       </c>
       <c r="J35" s="177" t="inlineStr"/>
       <c r="K35" s="177" t="inlineStr"/>
-      <c r="L35" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:692</t>
-        </is>
-      </c>
+      <c r="L35" s="177" t="inlineStr"/>
       <c r="M35" s="177" t="inlineStr"/>
     </row>
     <row r="36">
@@ -5837,11 +5701,7 @@
       </c>
       <c r="J36" s="177" t="inlineStr"/>
       <c r="K36" s="177" t="inlineStr"/>
-      <c r="L36" s="177" t="inlineStr">
-        <is>
-          <t>Manual (declared in spec as skip) — artifacts/qa-automation/tests/functional.spec.ts:711</t>
-        </is>
-      </c>
+      <c r="L36" s="177" t="inlineStr"/>
       <c r="M36" s="177" t="inlineStr"/>
     </row>
     <row r="37">
@@ -5888,11 +5748,7 @@
       </c>
       <c r="J37" s="177" t="inlineStr"/>
       <c r="K37" s="177" t="inlineStr"/>
-      <c r="L37" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:719</t>
-        </is>
-      </c>
+      <c r="L37" s="177" t="inlineStr"/>
       <c r="M37" s="177" t="inlineStr"/>
     </row>
     <row r="38">
@@ -5939,11 +5795,7 @@
       </c>
       <c r="J38" s="177" t="inlineStr"/>
       <c r="K38" s="177" t="inlineStr"/>
-      <c r="L38" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:740</t>
-        </is>
-      </c>
+      <c r="L38" s="177" t="inlineStr"/>
       <c r="M38" s="177" t="inlineStr"/>
     </row>
     <row r="39">
@@ -5990,11 +5842,7 @@
       </c>
       <c r="J39" s="177" t="inlineStr"/>
       <c r="K39" s="177" t="inlineStr"/>
-      <c r="L39" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:756</t>
-        </is>
-      </c>
+      <c r="L39" s="177" t="inlineStr"/>
       <c r="M39" s="177" t="inlineStr"/>
     </row>
     <row r="40">
@@ -6041,11 +5889,7 @@
       </c>
       <c r="J40" s="177" t="inlineStr"/>
       <c r="K40" s="177" t="inlineStr"/>
-      <c r="L40" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:777</t>
-        </is>
-      </c>
+      <c r="L40" s="177" t="inlineStr"/>
       <c r="M40" s="177" t="inlineStr"/>
     </row>
     <row r="41">
@@ -6093,11 +5937,7 @@
       </c>
       <c r="J41" s="177" t="inlineStr"/>
       <c r="K41" s="177" t="inlineStr"/>
-      <c r="L41" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:806</t>
-        </is>
-      </c>
+      <c r="L41" s="177" t="inlineStr"/>
       <c r="M41" s="177" t="inlineStr"/>
     </row>
     <row r="42">
@@ -6144,11 +5984,7 @@
       </c>
       <c r="J42" s="177" t="inlineStr"/>
       <c r="K42" s="177" t="inlineStr"/>
-      <c r="L42" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:827</t>
-        </is>
-      </c>
+      <c r="L42" s="177" t="inlineStr"/>
       <c r="M42" s="177" t="inlineStr"/>
     </row>
     <row r="43">
@@ -6196,11 +6032,7 @@
       </c>
       <c r="J43" s="177" t="inlineStr"/>
       <c r="K43" s="177" t="inlineStr"/>
-      <c r="L43" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:845</t>
-        </is>
-      </c>
+      <c r="L43" s="177" t="inlineStr"/>
       <c r="M43" s="177" t="inlineStr"/>
     </row>
     <row r="44">
@@ -6248,11 +6080,7 @@
       </c>
       <c r="J44" s="177" t="inlineStr"/>
       <c r="K44" s="177" t="inlineStr"/>
-      <c r="L44" s="177" t="inlineStr">
-        <is>
-          <t>Manual (declared in spec as skip) — artifacts/qa-automation/tests/functional.spec.ts:872</t>
-        </is>
-      </c>
+      <c r="L44" s="177" t="inlineStr"/>
       <c r="M44" s="177" t="inlineStr"/>
     </row>
     <row r="45">
@@ -6299,11 +6127,7 @@
       </c>
       <c r="J45" s="177" t="inlineStr"/>
       <c r="K45" s="177" t="inlineStr"/>
-      <c r="L45" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:878</t>
-        </is>
-      </c>
+      <c r="L45" s="177" t="inlineStr"/>
       <c r="M45" s="177" t="inlineStr"/>
     </row>
     <row r="46">
@@ -6351,11 +6175,7 @@
       </c>
       <c r="J46" s="177" t="inlineStr"/>
       <c r="K46" s="177" t="inlineStr"/>
-      <c r="L46" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:906</t>
-        </is>
-      </c>
+      <c r="L46" s="177" t="inlineStr"/>
       <c r="M46" s="177" t="inlineStr"/>
     </row>
     <row r="47">
@@ -6402,11 +6222,7 @@
       </c>
       <c r="J47" s="177" t="inlineStr"/>
       <c r="K47" s="177" t="inlineStr"/>
-      <c r="L47" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:932</t>
-        </is>
-      </c>
+      <c r="L47" s="177" t="inlineStr"/>
       <c r="M47" s="177" t="inlineStr"/>
     </row>
     <row r="48">
@@ -6453,11 +6269,7 @@
       </c>
       <c r="J48" s="177" t="inlineStr"/>
       <c r="K48" s="177" t="inlineStr"/>
-      <c r="L48" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:951</t>
-        </is>
-      </c>
+      <c r="L48" s="177" t="inlineStr"/>
       <c r="M48" s="177" t="inlineStr"/>
     </row>
     <row r="49">
@@ -6505,11 +6317,7 @@
       </c>
       <c r="J49" s="177" t="inlineStr"/>
       <c r="K49" s="177" t="inlineStr"/>
-      <c r="L49" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:963</t>
-        </is>
-      </c>
+      <c r="L49" s="177" t="inlineStr"/>
       <c r="M49" s="177" t="inlineStr"/>
     </row>
     <row r="50">
@@ -6557,11 +6365,7 @@
       </c>
       <c r="J50" s="177" t="inlineStr"/>
       <c r="K50" s="177" t="inlineStr"/>
-      <c r="L50" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/functional.spec.ts:991</t>
-        </is>
-      </c>
+      <c r="L50" s="177" t="inlineStr"/>
       <c r="M50" s="177" t="inlineStr"/>
     </row>
   </sheetData>

--- a/docs/test-plans/qapulse-functional-tests.xlsx
+++ b/docs/test-plans/qapulse-functional-tests.xlsx
@@ -1844,7 +1844,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="en-US"/>
               </a:p>
@@ -2190,7 +2190,7 @@
                 </a:defRPr>
               </a:pPr>
               <a:r>
-                <a:t/>
+                <a:t>None</a:t>
               </a:r>
               <a:endParaRPr lang="en-US"/>
             </a:p>
@@ -2267,7 +2267,7 @@
                 </a:defRPr>
               </a:pPr>
               <a:r>
-                <a:t/>
+                <a:t>None</a:t>
               </a:r>
               <a:endParaRPr lang="en-US"/>
             </a:p>
@@ -2300,7 +2300,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -2404,7 +2404,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -2458,7 +2458,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="en-US"/>
         </a:p>
@@ -4072,9 +4072,17 @@
           <t>Session restored from localStorage; still logged in</t>
         </is>
       </c>
-      <c r="J2" s="177" t="inlineStr"/>
+      <c r="J2" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K2" s="177" t="inlineStr"/>
-      <c r="L2" s="177" t="inlineStr"/>
+      <c r="L2" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (32.0s) || Last automated run: 2026-07-19 03:30 UTC — Passed (32.1s)</t>
+        </is>
+      </c>
       <c r="M2" s="177" t="inlineStr"/>
     </row>
     <row r="3">
@@ -4121,9 +4129,17 @@
           <t>Forced to change password before reaching the app</t>
         </is>
       </c>
-      <c r="J3" s="177" t="inlineStr"/>
+      <c r="J3" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K3" s="177" t="inlineStr"/>
-      <c r="L3" s="177" t="inlineStr"/>
+      <c r="L3" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (2.0s) || Last automated run: 2026-07-19 03:30 UTC — Passed (2.1s)</t>
+        </is>
+      </c>
       <c r="M3" s="177" t="inlineStr"/>
     </row>
     <row r="4">
@@ -4168,9 +4184,17 @@
           <t>Token cleared; redirected to /login; back-nav does not restore app</t>
         </is>
       </c>
-      <c r="J4" s="177" t="inlineStr"/>
+      <c r="J4" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K4" s="177" t="inlineStr"/>
-      <c r="L4" s="177" t="inlineStr"/>
+      <c r="L4" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (0.5s) || Last automated run: 2026-07-19 03:30 UTC — Passed (0.6s)</t>
+        </is>
+      </c>
       <c r="M4" s="177" t="inlineStr"/>
     </row>
     <row r="5">
@@ -4217,9 +4241,17 @@
           <t>Created in draft with all fields persisted; visible in list</t>
         </is>
       </c>
-      <c r="J5" s="177" t="inlineStr"/>
+      <c r="J5" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K5" s="177" t="inlineStr"/>
-      <c r="L5" s="177" t="inlineStr"/>
+      <c r="L5" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (0.8s) || Last automated run: 2026-07-19 03:30 UTC — Passed (0.8s)</t>
+        </is>
+      </c>
       <c r="M5" s="177" t="inlineStr"/>
     </row>
     <row r="6">
@@ -4264,9 +4296,17 @@
           <t>Child renders nested under parent; coverage rolls up (CR016)</t>
         </is>
       </c>
-      <c r="J6" s="177" t="inlineStr"/>
+      <c r="J6" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K6" s="177" t="inlineStr"/>
-      <c r="L6" s="177" t="inlineStr"/>
+      <c r="L6" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (0.4s) || Last automated run: 2026-07-19 03:30 UTC — Passed (0.6s)</t>
+        </is>
+      </c>
       <c r="M6" s="177" t="inlineStr"/>
     </row>
     <row r="7">
@@ -4313,9 +4353,17 @@
           <t>AC list persists and renders on detail</t>
         </is>
       </c>
-      <c r="J7" s="177" t="inlineStr"/>
+      <c r="J7" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K7" s="177" t="inlineStr"/>
-      <c r="L7" s="177" t="inlineStr"/>
+      <c r="L7" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (0.5s) || Last automated run: 2026-07-19 03:30 UTC — Passed (0.3s)</t>
+        </is>
+      </c>
       <c r="M7" s="177" t="inlineStr"/>
     </row>
     <row r="8">
@@ -4361,9 +4409,17 @@
           <t>Comment appears in the thread; author + timestamp shown</t>
         </is>
       </c>
-      <c r="J8" s="177" t="inlineStr"/>
+      <c r="J8" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K8" s="177" t="inlineStr"/>
-      <c r="L8" s="177" t="inlineStr"/>
+      <c r="L8" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (0.4s) || Last automated run: 2026-07-19 03:30 UTC — Passed (0.3s)</t>
+        </is>
+      </c>
       <c r="M8" s="177" t="inlineStr"/>
     </row>
     <row r="9">
@@ -4409,9 +4465,17 @@
           <t>Status draft-&gt;in_review-&gt;approved; history timeline logs each</t>
         </is>
       </c>
-      <c r="J9" s="177" t="inlineStr"/>
+      <c r="J9" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K9" s="177" t="inlineStr"/>
-      <c r="L9" s="177" t="inlineStr"/>
+      <c r="L9" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (0.5s) || Last automated run: 2026-07-19 03:30 UTC — Passed (0.5s)</t>
+        </is>
+      </c>
       <c r="M9" s="177" t="inlineStr"/>
     </row>
     <row r="10">
@@ -4458,9 +4522,17 @@
           <t>Re-enters review then approved; re-review flow works</t>
         </is>
       </c>
-      <c r="J10" s="177" t="inlineStr"/>
+      <c r="J10" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K10" s="177" t="inlineStr"/>
-      <c r="L10" s="177" t="inlineStr"/>
+      <c r="L10" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (0.8s) || Last automated run: 2026-07-19 03:30 UTC — Passed (0.8s)</t>
+        </is>
+      </c>
       <c r="M10" s="177" t="inlineStr"/>
     </row>
     <row r="11">
@@ -4505,9 +4577,17 @@
           <t>Auto-matches the relevant requirement (or asks when ambiguous)</t>
         </is>
       </c>
-      <c r="J11" s="177" t="inlineStr"/>
+      <c r="J11" s="177" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
       <c r="K11" s="177" t="inlineStr"/>
-      <c r="L11" s="177" t="inlineStr"/>
+      <c r="L11" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Not Executed (0.0s) || Last automated run: 2026-07-19 03:30 UTC — Not Executed (0.0s)</t>
+        </is>
+      </c>
       <c r="M11" s="177" t="inlineStr"/>
     </row>
     <row r="12">
@@ -4554,9 +4634,17 @@
           <t>List narrows correctly for each filter and combinations</t>
         </is>
       </c>
-      <c r="J12" s="177" t="inlineStr"/>
+      <c r="J12" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K12" s="177" t="inlineStr"/>
-      <c r="L12" s="177" t="inlineStr"/>
+      <c r="L12" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (1.0s) || Last automated run: 2026-07-19 03:30 UTC — Passed (2.9s)</t>
+        </is>
+      </c>
       <c r="M12" s="177" t="inlineStr"/>
     </row>
     <row r="13">
@@ -4603,9 +4691,17 @@
           <t>Only child issues of that tracker imported; root always imported</t>
         </is>
       </c>
-      <c r="J13" s="177" t="inlineStr"/>
+      <c r="J13" s="177" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
       <c r="K13" s="177" t="inlineStr"/>
-      <c r="L13" s="177" t="inlineStr"/>
+      <c r="L13" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Not Executed (0.0s) || Last automated run: 2026-07-19 03:30 UTC — Not Executed (0.0s)</t>
+        </is>
+      </c>
       <c r="M13" s="177" t="inlineStr"/>
     </row>
     <row r="14">
@@ -4650,9 +4746,17 @@
           <t>Unassigned (approved, no dev) and My Dev Work lists populate</t>
         </is>
       </c>
-      <c r="J14" s="177" t="inlineStr"/>
+      <c r="J14" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K14" s="177" t="inlineStr"/>
-      <c r="L14" s="177" t="inlineStr"/>
+      <c r="L14" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (1.2s) || Last automated run: 2026-07-19 03:30 UTC — Passed (0.7s)</t>
+        </is>
+      </c>
       <c r="M14" s="177" t="inlineStr"/>
     </row>
     <row r="15">
@@ -4699,9 +4803,17 @@
           <t>devStatus assigned -&gt; in_progress -&gt; ready_for_qa; each notifies</t>
         </is>
       </c>
-      <c r="J15" s="177" t="inlineStr"/>
+      <c r="J15" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K15" s="177" t="inlineStr"/>
-      <c r="L15" s="177" t="inlineStr"/>
+      <c r="L15" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (1.0s) || Last automated run: 2026-07-19 03:30 UTC — Passed (1.1s)</t>
+        </is>
+      </c>
       <c r="M15" s="177" t="inlineStr"/>
     </row>
     <row r="16">
@@ -4747,9 +4859,17 @@
           <t>devStatus -&gt; in_progress; dev + dev_lead notified; timeline resumes develop</t>
         </is>
       </c>
-      <c r="J16" s="177" t="inlineStr"/>
+      <c r="J16" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K16" s="177" t="inlineStr"/>
-      <c r="L16" s="177" t="inlineStr"/>
+      <c r="L16" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (1.1s) || Last automated run: 2026-07-19 03:30 UTC — Passed (1.1s)</t>
+        </is>
+      </c>
       <c r="M16" s="177" t="inlineStr"/>
     </row>
     <row r="17">
@@ -4795,9 +4915,17 @@
           <t>Status -&gt; rejected to author; FA notified; dev handoff reset; timeline new cycle</t>
         </is>
       </c>
-      <c r="J17" s="177" t="inlineStr"/>
+      <c r="J17" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K17" s="177" t="inlineStr"/>
-      <c r="L17" s="177" t="inlineStr"/>
+      <c r="L17" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (1.0s) || Last automated run: 2026-07-19 03:30 UTC — Passed (1.2s)</t>
+        </is>
+      </c>
       <c r="M17" s="177" t="inlineStr"/>
     </row>
     <row r="18">
@@ -4843,9 +4971,17 @@
           <t>TC saved to library; searchable</t>
         </is>
       </c>
-      <c r="J18" s="177" t="inlineStr"/>
+      <c r="J18" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K18" s="177" t="inlineStr"/>
-      <c r="L18" s="177" t="inlineStr"/>
+      <c r="L18" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (0.2s) || Last automated run: 2026-07-19 03:30 UTC — Passed (0.2s)</t>
+        </is>
+      </c>
       <c r="M18" s="177" t="inlineStr"/>
     </row>
     <row r="19">
@@ -4890,9 +5026,17 @@
           <t>Relevant TCs returned</t>
         </is>
       </c>
-      <c r="J19" s="177" t="inlineStr"/>
+      <c r="J19" s="177" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
       <c r="K19" s="177" t="inlineStr"/>
-      <c r="L19" s="177" t="inlineStr"/>
+      <c r="L19" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Not Executed (0.0s) || Last automated run: 2026-07-19 03:30 UTC — Not Executed (0.0s)</t>
+        </is>
+      </c>
       <c r="M19" s="177" t="inlineStr"/>
     </row>
     <row r="20">
@@ -4937,9 +5081,17 @@
           <t>Draft TCs generated and linkable to the requirement</t>
         </is>
       </c>
-      <c r="J20" s="177" t="inlineStr"/>
+      <c r="J20" s="177" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
       <c r="K20" s="177" t="inlineStr"/>
-      <c r="L20" s="177" t="inlineStr"/>
+      <c r="L20" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Not Executed (0.0s) || Last automated run: 2026-07-19 03:30 UTC — Not Executed (0.0s)</t>
+        </is>
+      </c>
       <c r="M20" s="177" t="inlineStr"/>
     </row>
     <row r="21">
@@ -4985,9 +5137,17 @@
           <t>Execution file created/updated, pre-populated from TC metadata</t>
         </is>
       </c>
-      <c r="J21" s="177" t="inlineStr"/>
+      <c r="J21" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K21" s="177" t="inlineStr"/>
-      <c r="L21" s="177" t="inlineStr"/>
+      <c r="L21" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (0.4s) || Last automated run: 2026-07-19 03:30 UTC — Passed (0.5s)</t>
+        </is>
+      </c>
       <c r="M21" s="177" t="inlineStr"/>
     </row>
     <row r="22">
@@ -5033,9 +5193,17 @@
           <t>Both created with correct type and milestone link</t>
         </is>
       </c>
-      <c r="J22" s="177" t="inlineStr"/>
+      <c r="J22" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K22" s="177" t="inlineStr"/>
-      <c r="L22" s="177" t="inlineStr"/>
+      <c r="L22" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (0.3s) || Last automated run: 2026-07-19 03:30 UTC — Passed (0.4s)</t>
+        </is>
+      </c>
       <c r="M22" s="177" t="inlineStr"/>
     </row>
     <row r="23">
@@ -5081,9 +5249,17 @@
           <t>Execute shows ResultPills; Edit allows structural changes; dirty indicator tracks unsaved</t>
         </is>
       </c>
-      <c r="J23" s="177" t="inlineStr"/>
+      <c r="J23" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K23" s="177" t="inlineStr"/>
-      <c r="L23" s="177" t="inlineStr"/>
+      <c r="L23" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (31.5s) || Last automated run: 2026-07-19 03:30 UTC — Passed (32.3s)</t>
+        </is>
+      </c>
       <c r="M23" s="177" t="inlineStr"/>
     </row>
     <row r="24">
@@ -5129,9 +5305,17 @@
           <t>Results persist; pass rate + counts update</t>
         </is>
       </c>
-      <c r="J24" s="177" t="inlineStr"/>
+      <c r="J24" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K24" s="177" t="inlineStr"/>
-      <c r="L24" s="177" t="inlineStr"/>
+      <c r="L24" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (1.0s) || Last automated run: 2026-07-19 03:30 UTC — Passed (0.9s)</t>
+        </is>
+      </c>
       <c r="M24" s="177" t="inlineStr"/>
     </row>
     <row r="25">
@@ -5176,9 +5360,17 @@
           <t>Same data rendered consistently in each view</t>
         </is>
       </c>
-      <c r="J25" s="177" t="inlineStr"/>
+      <c r="J25" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K25" s="177" t="inlineStr"/>
-      <c r="L25" s="177" t="inlineStr"/>
+      <c r="L25" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (37.6s) || Last automated run: 2026-07-19 03:30 UTC — Passed (41.8s)</t>
+        </is>
+      </c>
       <c r="M25" s="177" t="inlineStr"/>
     </row>
     <row r="26">
@@ -5223,9 +5415,17 @@
           <t>Review Log, Effort, Pareto, CAPA sheets auto-populated</t>
         </is>
       </c>
-      <c r="J26" s="177" t="inlineStr"/>
+      <c r="J26" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K26" s="177" t="inlineStr"/>
-      <c r="L26" s="177" t="inlineStr"/>
+      <c r="L26" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (1.6s) || Last automated run: 2026-07-19 03:30 UTC — Passed (1.8s)</t>
+        </is>
+      </c>
       <c r="M26" s="177" t="inlineStr"/>
     </row>
     <row r="27">
@@ -5272,9 +5472,17 @@
           <t>Email sent with Excel attachment; verdict recorded</t>
         </is>
       </c>
-      <c r="J27" s="177" t="inlineStr"/>
+      <c r="J27" s="177" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
       <c r="K27" s="177" t="inlineStr"/>
-      <c r="L27" s="177" t="inlineStr"/>
+      <c r="L27" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Not Executed (0.0s) || Last automated run: 2026-07-19 03:30 UTC — Not Executed (0.0s)</t>
+        </is>
+      </c>
       <c r="M27" s="177" t="inlineStr"/>
     </row>
     <row r="28">
@@ -5319,9 +5527,17 @@
           <t>Local defect + Redmine issue created; DEF-code assigned</t>
         </is>
       </c>
-      <c r="J28" s="177" t="inlineStr"/>
+      <c r="J28" s="177" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
       <c r="K28" s="177" t="inlineStr"/>
-      <c r="L28" s="177" t="inlineStr"/>
+      <c r="L28" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Not Executed (0.0s) || Last automated run: 2026-07-19 03:30 UTC — Not Executed (0.0s)</t>
+        </is>
+      </c>
       <c r="M28" s="177" t="inlineStr"/>
     </row>
     <row r="29">
@@ -5366,9 +5582,17 @@
           <t>assigneeId set; dev notified</t>
         </is>
       </c>
-      <c r="J29" s="177" t="inlineStr"/>
+      <c r="J29" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K29" s="177" t="inlineStr"/>
-      <c r="L29" s="177" t="inlineStr"/>
+      <c r="L29" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (0.6s) || Last automated run: 2026-07-19 03:30 UTC — Passed (1.3s)</t>
+        </is>
+      </c>
       <c r="M29" s="177" t="inlineStr"/>
     </row>
     <row r="30">
@@ -5414,9 +5638,17 @@
           <t>Retest-needed + reopen notifications fire to the right people</t>
         </is>
       </c>
-      <c r="J30" s="177" t="inlineStr"/>
+      <c r="J30" s="177" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
       <c r="K30" s="177" t="inlineStr"/>
-      <c r="L30" s="177" t="inlineStr"/>
+      <c r="L30" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Not Executed (0.2s) || Last automated run: 2026-07-19 03:30 UTC — Not Executed (0.2s)</t>
+        </is>
+      </c>
       <c r="M30" s="177" t="inlineStr"/>
     </row>
     <row r="31">
@@ -5462,9 +5694,17 @@
           <t>Tabs filter correctly; escape funnel + regression backfill shown</t>
         </is>
       </c>
-      <c r="J31" s="177" t="inlineStr"/>
+      <c r="J31" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K31" s="177" t="inlineStr"/>
-      <c r="L31" s="177" t="inlineStr"/>
+      <c r="L31" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (1.2s) || Last automated run: 2026-07-19 03:30 UTC — Passed (1.0s)</t>
+        </is>
+      </c>
       <c r="M31" s="177" t="inlineStr"/>
     </row>
     <row r="32">
@@ -5509,9 +5749,17 @@
           <t>Created with all phase dates + ENV; appears on dashboards</t>
         </is>
       </c>
-      <c r="J32" s="177" t="inlineStr"/>
+      <c r="J32" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K32" s="177" t="inlineStr"/>
-      <c r="L32" s="177" t="inlineStr"/>
+      <c r="L32" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (0.3s) || Last automated run: 2026-07-19 03:30 UTC — Passed (0.3s)</t>
+        </is>
+      </c>
       <c r="M32" s="177" t="inlineStr"/>
     </row>
     <row r="33">
@@ -5557,9 +5805,17 @@
           <t>Status completed; closedBy + lessons stored; Closing panel updates</t>
         </is>
       </c>
-      <c r="J33" s="177" t="inlineStr"/>
+      <c r="J33" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K33" s="177" t="inlineStr"/>
-      <c r="L33" s="177" t="inlineStr"/>
+      <c r="L33" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (0.2s) || Last automated run: 2026-07-19 03:30 UTC — Passed (0.2s)</t>
+        </is>
+      </c>
       <c r="M33" s="177" t="inlineStr"/>
     </row>
     <row r="34">
@@ -5605,9 +5861,17 @@
           <t>Plan + Actual bars, variance chips, multi-cycle phases render</t>
         </is>
       </c>
-      <c r="J34" s="177" t="inlineStr"/>
+      <c r="J34" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K34" s="177" t="inlineStr"/>
-      <c r="L34" s="177" t="inlineStr"/>
+      <c r="L34" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (0.5s) || Last automated run: 2026-07-19 03:30 UTC — Passed (0.6s)</t>
+        </is>
+      </c>
       <c r="M34" s="177" t="inlineStr"/>
     </row>
     <row r="35">
@@ -5652,9 +5916,17 @@
           <t>Each computes and renders with correct severity coloring</t>
         </is>
       </c>
-      <c r="J35" s="177" t="inlineStr"/>
+      <c r="J35" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K35" s="177" t="inlineStr"/>
-      <c r="L35" s="177" t="inlineStr"/>
+      <c r="L35" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (0.6s) || Last automated run: 2026-07-19 03:30 UTC — Passed (0.7s)</t>
+        </is>
+      </c>
       <c r="M35" s="177" t="inlineStr"/>
     </row>
     <row r="36">
@@ -5699,9 +5971,17 @@
           <t>Risk card returns level + rationale; stored in history</t>
         </is>
       </c>
-      <c r="J36" s="177" t="inlineStr"/>
+      <c r="J36" s="177" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
       <c r="K36" s="177" t="inlineStr"/>
-      <c r="L36" s="177" t="inlineStr"/>
+      <c r="L36" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Not Executed (0.0s) || Last automated run: 2026-07-19 03:30 UTC — Not Executed (0.0s)</t>
+        </is>
+      </c>
       <c r="M36" s="177" t="inlineStr"/>
     </row>
     <row r="37">
@@ -5746,9 +6026,17 @@
           <t>Risk saved and listed; reachable by qa_lead/fa_lead too (CR040)</t>
         </is>
       </c>
-      <c r="J37" s="177" t="inlineStr"/>
+      <c r="J37" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K37" s="177" t="inlineStr"/>
-      <c r="L37" s="177" t="inlineStr"/>
+      <c r="L37" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (30.6s) || Last automated run: 2026-07-19 03:30 UTC — Passed (34.8s)</t>
+        </is>
+      </c>
       <c r="M37" s="177" t="inlineStr"/>
     </row>
     <row r="38">
@@ -5793,9 +6081,17 @@
           <t>User created (hashed password); can log in</t>
         </is>
       </c>
-      <c r="J38" s="177" t="inlineStr"/>
+      <c r="J38" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K38" s="177" t="inlineStr"/>
-      <c r="L38" s="177" t="inlineStr"/>
+      <c r="L38" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (1.3s) || Last automated run: 2026-07-19 03:30 UTC — Passed (1.4s)</t>
+        </is>
+      </c>
       <c r="M38" s="177" t="inlineStr"/>
     </row>
     <row r="39">
@@ -5840,9 +6136,17 @@
           <t>Member sees all modules of the project</t>
         </is>
       </c>
-      <c r="J39" s="177" t="inlineStr"/>
+      <c r="J39" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K39" s="177" t="inlineStr"/>
-      <c r="L39" s="177" t="inlineStr"/>
+      <c r="L39" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (1.5s) || Last automated run: 2026-07-19 03:30 UTC — Passed (1.5s)</t>
+        </is>
+      </c>
       <c r="M39" s="177" t="inlineStr"/>
     </row>
     <row r="40">
@@ -5887,9 +6191,17 @@
           <t>Member sees only those 2 modules' records</t>
         </is>
       </c>
-      <c r="J40" s="177" t="inlineStr"/>
+      <c r="J40" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K40" s="177" t="inlineStr"/>
-      <c r="L40" s="177" t="inlineStr"/>
+      <c r="L40" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (1.6s) || Last automated run: 2026-07-19 03:30 UTC — Passed (1.6s)</t>
+        </is>
+      </c>
       <c r="M40" s="177" t="inlineStr"/>
     </row>
     <row r="41">
@@ -5935,9 +6247,17 @@
           <t>Live permission matrix + RACI letters + gap flags render</t>
         </is>
       </c>
-      <c r="J41" s="177" t="inlineStr"/>
+      <c r="J41" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K41" s="177" t="inlineStr"/>
-      <c r="L41" s="177" t="inlineStr"/>
+      <c r="L41" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (33.0s) || Last automated run: 2026-07-19 03:30 UTC — Passed (30.4s)</t>
+        </is>
+      </c>
       <c r="M41" s="177" t="inlineStr"/>
     </row>
     <row r="42">
@@ -5982,9 +6302,17 @@
           <t>Bell updates in near real-time without manual refresh</t>
         </is>
       </c>
-      <c r="J42" s="177" t="inlineStr"/>
+      <c r="J42" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K42" s="177" t="inlineStr"/>
-      <c r="L42" s="177" t="inlineStr"/>
+      <c r="L42" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (34.3s) || Last automated run: 2026-07-19 03:30 UTC — Passed (32.1s)</t>
+        </is>
+      </c>
       <c r="M42" s="177" t="inlineStr"/>
     </row>
     <row r="43">
@@ -6030,9 +6358,17 @@
           <t>Filter works; click navigates to the entity (row focus where supported)</t>
         </is>
       </c>
-      <c r="J43" s="177" t="inlineStr"/>
+      <c r="J43" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K43" s="177" t="inlineStr"/>
-      <c r="L43" s="177" t="inlineStr"/>
+      <c r="L43" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (31.5s) || Last automated run: 2026-07-19 03:30 UTC — Passed (29.5s)</t>
+        </is>
+      </c>
       <c r="M43" s="177" t="inlineStr"/>
     </row>
     <row r="44">
@@ -6078,9 +6414,17 @@
           <t>Contact saved; Redmine sync imports names/emails</t>
         </is>
       </c>
-      <c r="J44" s="177" t="inlineStr"/>
+      <c r="J44" s="177" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
       <c r="K44" s="177" t="inlineStr"/>
-      <c r="L44" s="177" t="inlineStr"/>
+      <c r="L44" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Not Executed (0.0s) || Last automated run: 2026-07-19 03:30 UTC — Not Executed (0.0s)</t>
+        </is>
+      </c>
       <c r="M44" s="177" t="inlineStr"/>
     </row>
     <row r="45">
@@ -6125,9 +6469,17 @@
           <t>Entries persist and list correctly</t>
         </is>
       </c>
-      <c r="J45" s="177" t="inlineStr"/>
+      <c r="J45" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K45" s="177" t="inlineStr"/>
-      <c r="L45" s="177" t="inlineStr"/>
+      <c r="L45" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (1.1s) || Last automated run: 2026-07-19 03:30 UTC — Passed (1.1s)</t>
+        </is>
+      </c>
       <c r="M45" s="177" t="inlineStr"/>
     </row>
     <row r="46">
@@ -6173,9 +6525,17 @@
           <t>Activity entries with actor, diff, timestamp shown</t>
         </is>
       </c>
-      <c r="J46" s="177" t="inlineStr"/>
+      <c r="J46" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K46" s="177" t="inlineStr"/>
-      <c r="L46" s="177" t="inlineStr"/>
+      <c r="L46" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (0.3s) || Last automated run: 2026-07-19 03:30 UTC — Passed (0.2s)</t>
+        </is>
+      </c>
       <c r="M46" s="177" t="inlineStr"/>
     </row>
     <row r="47">
@@ -6220,9 +6580,17 @@
           <t>Execution trend, velocity, pass-by-milestone, defect density/escape render</t>
         </is>
       </c>
-      <c r="J47" s="177" t="inlineStr"/>
+      <c r="J47" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K47" s="177" t="inlineStr"/>
-      <c r="L47" s="177" t="inlineStr"/>
+      <c r="L47" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (34.7s) || Last automated run: 2026-07-19 03:30 UTC — Passed (31.3s)</t>
+        </is>
+      </c>
       <c r="M47" s="177" t="inlineStr"/>
     </row>
     <row r="48">
@@ -6267,9 +6635,17 @@
           <t>Active/idle/closed milestone focus + utilization % (Dev/PM) render</t>
         </is>
       </c>
-      <c r="J48" s="177" t="inlineStr"/>
+      <c r="J48" s="177" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
       <c r="K48" s="177" t="inlineStr"/>
-      <c r="L48" s="177" t="inlineStr"/>
+      <c r="L48" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Not Executed (0.7s) || Last automated run: 2026-07-19 03:30 UTC — Not Executed (0.7s)</t>
+        </is>
+      </c>
       <c r="M48" s="177" t="inlineStr"/>
     </row>
     <row r="49">
@@ -6315,9 +6691,17 @@
           <t>Req -&gt; TC -&gt; execution result matrix; grouped; Excel export works</t>
         </is>
       </c>
-      <c r="J49" s="177" t="inlineStr"/>
+      <c r="J49" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K49" s="177" t="inlineStr"/>
-      <c r="L49" s="177" t="inlineStr"/>
+      <c r="L49" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (1.1s) || Last automated run: 2026-07-19 03:30 UTC — Passed (1.2s)</t>
+        </is>
+      </c>
       <c r="M49" s="177" t="inlineStr"/>
     </row>
     <row r="50">
@@ -6363,9 +6747,17 @@
           <t>Self-contained PMO portal renders; can send report/verdict</t>
         </is>
       </c>
-      <c r="J50" s="177" t="inlineStr"/>
+      <c r="J50" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K50" s="177" t="inlineStr"/>
-      <c r="L50" s="177" t="inlineStr"/>
+      <c r="L50" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (28.4s) || Last automated run: 2026-07-19 03:30 UTC — Passed (33.1s)</t>
+        </is>
+      </c>
       <c r="M50" s="177" t="inlineStr"/>
     </row>
   </sheetData>
